--- a/samples/components-template.xlsx
+++ b/samples/components-template.xlsx
@@ -707,7 +707,7 @@
   <autoFilter ref="A1:C15"/>
   <dataValidations count="2">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Type không hợp lệ" error="Type không nằm trong danh sách. Xem sheet DanhMucType, hoặc điền số component type." type="list" errorStyle="warning">
-      <formula1>=DanhMucType!$A$2:$A$30</formula1>
+      <formula1>=DanhMucType!$A$2:$A$31</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="IncludeAll không hợp lệ" error="Chỉ nhận Y hoặc N (để trống = N)." type="list" errorStyle="warning">
       <formula1>"Y,N"</formula1>
@@ -1283,7 +1283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C30"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1515,6 +1515,13 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
